--- a/05. Res/modelos/metricas_clasificacion_logit.xlsx
+++ b/05. Res/modelos/metricas_clasificacion_logit.xlsx
@@ -439,31 +439,31 @@
         <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.857844294414806</v>
+        <v>0.862852038177629</v>
       </c>
       <c r="D2" t="n">
-        <v>0.42418235877106</v>
+        <v>0.446653246099648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.959930008748906</v>
+        <v>0.958485111303845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.713630679449771</v>
+        <v>0.711993582029683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.532090132090132</v>
+        <v>0.548940776248647</v>
       </c>
       <c r="H2" t="n">
-        <v>0.911188036166771</v>
+        <v>0.913175566012851</v>
       </c>
       <c r="I2" t="n">
-        <v>0.325525287435525</v>
+        <v>0.322135637186654</v>
       </c>
       <c r="J2" t="n">
-        <v>0.190548132760493</v>
+        <v>0.186844703559171</v>
       </c>
       <c r="K2" t="n">
-        <v>0.187706975726861</v>
+        <v>0.192360288975075</v>
       </c>
     </row>
   </sheetData>
